--- a/NNs/Graph NNs/Data.xlsx
+++ b/NNs/Graph NNs/Data.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17850" windowHeight="11310" activeTab="2"/>
   </bookViews>
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -815,7 +815,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
   </numFmts>
@@ -883,7 +883,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1162,12 +1162,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>364.45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <f>1000*(1000*0.01)/B1</f>
         <v>27.438606118809165</v>
@@ -1184,7 +1184,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.1</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>4.4642857142857144</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.2</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>8.9285714285714288</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.3</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>13.392857142857142</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.35</v>
       </c>
@@ -1236,12 +1236,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1">
         <v>302.92090804548701</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>241487.88800838901</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>302.92729673324999</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>141366.699530613</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>302.93837045870703</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>55880.915436266907</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>303.05975552621402</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>21322.938524639198</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>302.97244346011303</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>3213.7068680277603</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>303.73866007921902</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>41.373410807913601</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>304.05085395459702</v>
       </c>
@@ -1333,18 +1333,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H606"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.1796875" customWidth="1"/>
+    <col min="2" max="2" width="48.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" customWidth="1"/>
-    <col min="8" max="8" width="28.28515625" customWidth="1"/>
+    <col min="4" max="5" width="23.1796875" customWidth="1"/>
+    <col min="6" max="6" width="28.81640625" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" customWidth="1"/>
+    <col min="8" max="8" width="28.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>1.04477745095757</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>1.94720301577807</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>3.7072923637694997</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>68.649642579641593</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>7631.2102120417603</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>40640</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>2.9816217976770303</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>6.5143128711216898</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>239.64150798318201</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>911.70432407783301</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>2907.3923918903997</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>7205.5018426732695</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>2499.25298209318</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>803.72872297179401</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>1.7794725491957899</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>2.2585137927935999</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>1.62930182406325</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>2.6432069368316902</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>3.5445682451253502</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>4.2582442267948597</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>3.7702174499056502</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>3.3850750292029801</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>2.29569143678677</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>9.5073681372989505</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>5.0378515589900204</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>2.8682945457812901</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>16.981647048252299</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>11.385344595201699</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>5.5073456734657196</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>4.08931620091652</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>2.6246742744181799</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>10.86</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>20</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>2.0144924705560601</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>2.5997089786909902</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>34</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>5.1610383015293202</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>12.8984941112131</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>34</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>2.1975062645291699</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>34</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>2.5574978111885902</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>34</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>5.1472390785858702</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>21.5740120158198</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>36</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>2.6716135686454501</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>36</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>5.3518221407288697</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>36</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>8.0005157002062699</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>36</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>18.633967453586902</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>42.013809305523601</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>36</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>291.19728397891299</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>36</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>4.2621723636209996</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>36</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>1.87535583999323</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>36</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>16.801657423612902</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>36</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>331.01944204288998</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>39</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>13978</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>54</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>39.81</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>42</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>42</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>42</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>42</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>42</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>44</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>44</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>44</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>44</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>44</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>44</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>42</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>42</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>42</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>44</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>42</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>44</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>46</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>46</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>141629</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>46</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>1015606</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>46</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>6203000</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>46</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>46</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>46</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>60</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>60</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>60</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>60</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>60</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>60</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>50</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>50</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>50</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>61</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>61</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>61</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>61</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>63</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>83.87</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>63</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>63</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>63</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>65</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>65</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>67</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>68</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>71</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>73</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>75</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>10.7006895569317</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>48</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>11.3539521295368</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>48</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>80.243851346073896</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>48</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>7249.2673666503497</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>48</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>195.182634871197</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>77</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>16.201634239927099</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>77</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>548239.83516736701</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>77</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>1690211.98337871</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>77</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>1052104.3676924801</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>79</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>601.74399458955395</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>79</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>934519.214560539</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>79</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>991570.34411669197</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>79</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>77572.159605721594</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>81</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>4.9528245211413395</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>81</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>617221.68590598903</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>81</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>9188.3026986310797</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>81</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>5719.4325303422102</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>82</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>35.003997734299794</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>82</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>2273095.3160389601</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>82</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>177827.94100389199</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>84</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>11.3539521295368</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>84</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>3056990.7009353801</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>84</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>3560.16878656058</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>84</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>20.535250264571502</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>86</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>173.368658316416</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>86</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>991570.34411669197</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>86</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>2351.3838413522003</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>86</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>11645.9915480647</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>88</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>90</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>93</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>94</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>96</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>98</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>100</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>100</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>3277.1682340647999</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>100</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>19008.620689655101</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>100</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>47887.931034482695</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>100</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>56854.754440961304</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>100</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>57843.521421107602</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>100</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>2931.9767567450499</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>100</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>19770.3756507463</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>100</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>42448.750351024901</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>100</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>55983.194003412995</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>100</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>64697.254444516402</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>100</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>29077.398310759701</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>104</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>104</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>104</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>104</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>108</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>109</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>110</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>111</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>115</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>116</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>117</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>118</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>119</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>125</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>125</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>125</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>125</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>125</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>125</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>125</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>125</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>125</v>
       </c>
@@ -6529,7 +6529,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>125</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>125</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>127</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>127</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>127</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>127</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>127</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>127</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>127</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>10.31</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>127</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>127</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>127</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>127</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>127</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>127</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>129</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>129</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>129</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>129</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>129</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>129</v>
       </c>
@@ -7096,7 +7096,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>129</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>129</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>129</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>129</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>129</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>129</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>129</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>129</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>131</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>1.1838284581815901</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>131</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>1.23209162018893</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>131</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>1.29751506218585</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>131</v>
       </c>
@@ -7420,7 +7420,7 @@
         <v>1.3865479972319901</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>133</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>1.27411052892479</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>133</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>1.2596441504054099</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>133</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>1.48532087583343</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>133</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>1.59513257664355</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>135</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>135</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>137</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>116.06568382618499</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>137</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>3546.9760687242901</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>137</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>10223.477540370601</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>137</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>14667.6309475953</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>137</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>16.128329844736999</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>137</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>166.748512514807</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>137</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>1126.2214965519599</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>137</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>4089.1005635004999</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>137</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>4.9898045456805997</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>137</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>15.081066295319999</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>137</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>19.786890137762899</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>137</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>24.648629830407302</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>139</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>130.25776596716</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>139</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>2858.86306259094</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>139</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>8116.4395588012103</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>139</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>15826.896794927499</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>139</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>16.849464491854501</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>139</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>224.10583906743699</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>139</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>1189.9499659271701</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>139</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>6587.6591111673197</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>139</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>2.7998186967861498</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>139</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>26.667473556237699</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>139</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>135.80961360485401</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>139</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>817.30980106468496</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>141</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>166.31454521231399</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>141</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>1143.24559024269</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>141</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>14942.339672144</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>141</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>11742.685834509201</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>141</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>23.242298245944301</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>141</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>248.51284269805601</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>141</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>1851.15106175405</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>141</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>3814.1287482832099</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>141</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>5.4748483378970203</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>141</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>115.865326124376</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>141</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>269.29764661463599</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>141</v>
       </c>
@@ -8554,7 +8554,7 @@
         <v>1190.0943554067701</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>143</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>19.2962357090762</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>143</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>257.68141180412198</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>143</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>424.88943084066602</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>143</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>1805.8411353199201</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>143</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>3.9792579046113898</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>143</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>37.267327266961601</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>143</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>225.89777895757001</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>143</v>
       </c>
@@ -8770,7 +8770,7 @@
         <v>257.73823806889197</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>143</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>5.0425784541237197</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>143</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>23.1971999939684</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>143</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>80.933881052414193</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>143</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>97.317087306991198</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>147</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>147</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>147</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>147</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>147</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>147</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>147</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>147</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>147</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>147</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>148</v>
       </c>
@@ -9175,7 +9175,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>148</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>148</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>148</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>148</v>
       </c>
@@ -9283,7 +9283,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>148</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>148</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>148</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>149</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>149</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>149</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>149</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>149</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>149</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>152</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>0.769657270213014</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>152</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>2.3618053543316702</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>152</v>
       </c>
@@ -9611,7 +9611,7 @@
         <v>22314.9173309529</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>152</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>52961.431326218197</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>152</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>152</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>1.3433081483906499</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>152</v>
       </c>
@@ -9719,7 +9719,7 @@
         <v>41.901632747734297</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>152</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>551.32212006895395</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>152</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>1.4167116853680999</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>152</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>1.3433081483906499</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>152</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>41.901632747734297</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>152</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>551.32212006895395</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>152</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>1.2605550464622299</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>152</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>1.1244496684140899</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>152</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>1.0474903402498099</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>152</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>0.95486974360386601</v>
       </c>
     </row>
-    <row r="319" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>153</v>
       </c>
@@ -9989,7 +9989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>153</v>
       </c>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>153</v>
       </c>
@@ -10043,7 +10043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>153</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>156</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>3.5480937979510601</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>156</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>3.78971541987287</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>156</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>4.4497016139996797</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>156</v>
       </c>
@@ -10178,7 +10178,7 @@
         <v>6.4779987633229101</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>157</v>
       </c>
@@ -10205,7 +10205,7 @@
         <v>3.6937095494018402</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>157</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>4.5629651764153696</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>157</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>8.2728080965435904</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>159</v>
       </c>
@@ -10286,7 +10286,7 @@
         <v>3.6137047586639901</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>159</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>4.1815462850892899</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>159</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>6.3383987284507999</v>
       </c>
     </row>
-    <row r="333" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>161</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>161</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>163</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>163</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>13.07</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>165</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>165</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>165</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>165</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>19.190000000000001</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>167</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>167</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>167</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>167</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>169</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>169</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>169</v>
       </c>
@@ -10745,7 +10745,7 @@
         <v>10.45</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>171</v>
       </c>
@@ -10772,7 +10772,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>171</v>
       </c>
@@ -10799,7 +10799,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>171</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>171</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>173</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>173</v>
       </c>
@@ -10907,7 +10907,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>173</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>175</v>
       </c>
@@ -10961,7 +10961,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>175</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>175</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>177</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>177</v>
       </c>
@@ -11069,7 +11069,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>177</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>179</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>179</v>
       </c>
@@ -11150,7 +11150,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>179</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>179</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>181</v>
       </c>
@@ -11231,7 +11231,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>181</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>181</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="368" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>183</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>1.5216214557316701</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>183</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>42.768647950025802</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>183</v>
       </c>
@@ -11366,7 +11366,7 @@
         <v>1245.96883400351</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>183</v>
       </c>
@@ -11393,7 +11393,7 @@
         <v>14410.683376041901</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>185</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>187</v>
       </c>
@@ -11447,7 +11447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>189</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>1.1898395721925099</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>189</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>1.5534759358288699</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>189</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>1.9812834224598901</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>189</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>2.22727272727272</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>191</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>191</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>191</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>191</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>191</v>
       </c>
@@ -11690,7 +11690,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>191</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>191</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>191</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>191</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>191</v>
       </c>
@@ -11825,7 +11825,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>191</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>191</v>
       </c>
@@ -11879,7 +11879,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="390" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>96</v>
       </c>
@@ -11906,7 +11906,7 @@
         <v>1.4307229891937501</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>96</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>8.5769589859089397</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>96</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>4410.0594541767405</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>96</v>
       </c>
@@ -11987,7 +11987,7 @@
         <v>378248.99063893902</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>193</v>
       </c>
@@ -12014,7 +12014,7 @@
         <v>1.5058363542798401</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>193</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>3.0823992397451501</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>193</v>
       </c>
@@ -12068,7 +12068,7 @@
         <v>238.65897868585802</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>193</v>
       </c>
@@ -12095,7 +12095,7 @@
         <v>39810.717055349698</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>88</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>1.58489319246111</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>88</v>
       </c>
@@ -12149,7 +12149,7 @@
         <v>21.5443469003188</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>88</v>
       </c>
@@ -12176,7 +12176,7 @@
         <v>2154.4346900318797</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>88</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>175567.6291275</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>90</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>1.35935639087852</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>90</v>
       </c>
@@ -12257,7 +12257,7 @@
         <v>11.659144011798301</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>90</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>488.52735715193802</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>90</v>
       </c>
@@ -12311,7 +12311,7 @@
         <v>135935.639087852</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>195</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>1.7556762912750001</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>195</v>
       </c>
@@ -12365,7 +12365,7 @@
         <v>9.5011850731814302</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>195</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>90.272517794845697</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>195</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>194486.24389373601</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>196</v>
       </c>
@@ -12446,7 +12446,7 @@
         <v>1.2031003019517901</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>196</v>
       </c>
@@ -12473,7 +12473,7 @@
         <v>1.7756297160536001</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>196</v>
       </c>
@@ -12500,7 +12500,7 @@
         <v>25.601575761673399</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>196</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>4023.2089338893202</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>197</v>
       </c>
@@ -12554,7 +12554,7 @@
         <v>1.1811510484746299</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>197</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>2.45801497990908</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>197</v>
       </c>
@@ -12608,7 +12608,7 @@
         <v>578.27627603924202</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>197</v>
       </c>
@@ -12635,7 +12635,7 @@
         <v>75513.883368275405</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>199</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>1.2987522053070799</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>199</v>
       </c>
@@ -12689,7 +12689,7 @@
         <v>14.210431830705099</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>199</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>3163.5080064568401</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>199</v>
       </c>
@@ -12743,7 +12743,7 @@
         <v>36913.139916211898</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>201</v>
       </c>
@@ -12770,7 +12770,7 @@
         <v>1.4347439811676101</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>201</v>
       </c>
@@ -12797,7 +12797,7 @@
         <v>11.133375896041201</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>201</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>143.51161006070799</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>201</v>
       </c>
@@ -12851,7 +12851,7 @@
         <v>5177.9398327663394</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>203</v>
       </c>
@@ -12878,7 +12878,7 @@
         <v>1.69289237996942</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>203</v>
       </c>
@@ -12905,7 +12905,7 @@
         <v>5.9439295993342798</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>203</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>1781.1639971033399</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>203</v>
       </c>
@@ -12959,7 +12959,7 @@
         <v>105460.101651629</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>207</v>
       </c>
@@ -12986,7 +12986,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>213</v>
       </c>
@@ -13013,7 +13013,7 @@
         <v>77781</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>214</v>
       </c>
@@ -13040,7 +13040,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>212</v>
       </c>
@@ -13067,7 +13067,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>212</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>217</v>
       </c>
@@ -13121,7 +13121,7 @@
         <v>14008</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>217</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="437" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>220</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>1.0178699841461201</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>213</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>70.170382867038199</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>214</v>
       </c>
@@ -13229,7 +13229,7 @@
         <v>1.0360593046256299</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>220</v>
       </c>
@@ -13256,7 +13256,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>213</v>
       </c>
@@ -13283,7 +13283,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>214</v>
       </c>
@@ -13310,7 +13310,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>221</v>
       </c>
@@ -13337,7 +13337,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="444" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>104</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>1.99335963763758</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>104</v>
       </c>
@@ -13391,7 +13391,7 @@
         <v>78.323663383600092</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>104</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>2891.8660056705598</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>104</v>
       </c>
@@ -13445,7 +13445,7 @@
         <v>538.09543123252899</v>
       </c>
     </row>
-    <row r="448" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>189</v>
       </c>
@@ -13472,7 +13472,7 @@
         <v>1.1849379419472801</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>189</v>
       </c>
@@ -13499,7 +13499,7 @@
         <v>1.2764179399693401</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>189</v>
       </c>
@@ -13526,7 +13526,7 @@
         <v>1.7026652821045301</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>189</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>1.98125896256737</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>223</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>1.23992647058823</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>223</v>
       </c>
@@ -13607,7 +13607,7 @@
         <v>1.28426470588235</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>223</v>
       </c>
@@ -13634,7 +13634,7 @@
         <v>1.3806617647058801</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>223</v>
       </c>
@@ -13661,7 +13661,7 @@
         <v>2.07794117647058</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>224</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>1.5194805194805301</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>224</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>1.9285714285714399</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>224</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>7.0324675324675603</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>224</v>
       </c>
@@ -13769,7 +13769,7 @@
         <v>21.837662337662302</v>
       </c>
     </row>
-    <row r="460" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>227</v>
       </c>
@@ -13796,7 +13796,7 @@
         <v>0.74584182366527296</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>227</v>
       </c>
@@ -13823,7 +13823,7 @@
         <v>3.5793333012226598</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>227</v>
       </c>
@@ -13850,7 +13850,7 @@
         <v>9.4987626481452594</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>227</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>13.960064096812699</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>227</v>
       </c>
@@ -13904,7 +13904,7 @@
         <v>19.409815629279201</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>228</v>
       </c>
@@ -13931,7 +13931,7 @@
         <v>166.45596868565499</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>228</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>520.81696648636103</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>228</v>
       </c>
@@ -13985,7 +13985,7 @@
         <v>688.71551574473199</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>228</v>
       </c>
@@ -14012,7 +14012,7 @@
         <v>1189.0832334946299</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>228</v>
       </c>
@@ -14039,7 +14039,7 @@
         <v>1955.0555390100601</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>230</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>2.0175173385931702</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>230</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>41.375237018105402</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>230</v>
       </c>
@@ -14120,7 +14120,7 @@
         <v>249.04147906440599</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>230</v>
       </c>
@@ -14147,7 +14147,7 @@
         <v>453.338949928906</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>230</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>923.40693950386697</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>232</v>
       </c>
@@ -14201,7 +14201,7 @@
         <v>6.9135482265033499</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>232</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>15.774342766336</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>232</v>
       </c>
@@ -14255,7 +14255,7 @@
         <v>28.904366487440299</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>232</v>
       </c>
@@ -14282,7 +14282,7 @@
         <v>47.837792782336997</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>232</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>83.050629948071006</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>234</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>448.73852437471999</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>234</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>2031.7144993474001</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>234</v>
       </c>
@@ -14390,7 +14390,7 @@
         <v>4823.5884582773297</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>234</v>
       </c>
@@ -14417,7 +14417,7 @@
         <v>9237.9945979315198</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>235</v>
       </c>
@@ -14444,7 +14444,7 @@
         <v>51.280035883796202</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>235</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>57.944494917161599</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>235</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>52.716354194730201</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>235</v>
       </c>
@@ -14525,7 +14525,7 @@
         <v>81.720172141979106</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>235</v>
       </c>
@@ -14552,7 +14552,7 @@
         <v>134.33334578345401</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>236</v>
       </c>
@@ -14579,7 +14579,7 @@
         <v>1.1630826116569999</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>236</v>
       </c>
@@ -14606,7 +14606,7 @@
         <v>2.0388245596963994</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>236</v>
       </c>
@@ -14633,7 +14633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>236</v>
       </c>
@@ -14660,7 +14660,7 @@
         <v>41.447212221465101</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>236</v>
       </c>
@@ -14687,7 +14687,7 @@
         <v>1117.56378320521</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>236</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>1.1548195013025699</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>236</v>
       </c>
@@ -14741,7 +14741,7 @@
         <v>4.9880908075921102</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>236</v>
       </c>
@@ -14768,7 +14768,7 @@
         <v>12.9374767398585</v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>236</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>33.4808336434685</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>236</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>32.848157796799399</v>
       </c>
     </row>
-    <row r="499" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>238</v>
       </c>
@@ -14849,7 +14849,7 @@
         <v>2.7169652855542998</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>238</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>3.2362821948488198</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>238</v>
       </c>
@@ -14903,7 +14903,7 @@
         <v>5.12597984322508</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>238</v>
       </c>
@@ -14930,7 +14930,7 @@
         <v>11.279395296752501</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>241</v>
       </c>
@@ -14957,7 +14957,7 @@
         <v>1.66853303471444</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>241</v>
       </c>
@@ -14984,7 +14984,7 @@
         <v>2.0646696528555402</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>241</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>3.74160134378499</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>241</v>
       </c>
@@ -15038,7 +15038,7 @@
         <v>6.1744120940649401</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>238</v>
       </c>
@@ -15066,7 +15066,7 @@
         <v>1.56766381766381</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>238</v>
       </c>
@@ -15094,7 +15094,7 @@
         <v>2.0544871794871802</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>238</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>3.2628205128205101</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>238</v>
       </c>
@@ -15150,7 +15150,7 @@
         <v>4.8511396011396002</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>61</v>
       </c>
@@ -15177,7 +15177,7 @@
         <v>218.688060477927</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>61</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>44635.386560450599</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>61</v>
       </c>
@@ -15231,7 +15231,7 @@
         <v>339413.30524752499</v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>61</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>311382.68605517503</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>63</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>89.599009159852798</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>63</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>2539.0118220981599</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>63</v>
       </c>
@@ -15339,7 +15339,7 @@
         <v>29470.5170255181</v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>63</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>52199.655700525298</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>65</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>150.24256966487201</v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>65</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>38766.340899539602</v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>65</v>
       </c>
@@ -15447,7 +15447,7 @@
         <v>308718.51904743398</v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>65</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>358332.099618259</v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>61</v>
       </c>
@@ -15501,7 +15501,7 @@
         <v>80.662628855640307</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>61</v>
       </c>
@@ -15528,7 +15528,7 @@
         <v>372.75680879226701</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>61</v>
       </c>
@@ -15555,7 +15555,7 @@
         <v>252.809754923589</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>63</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>89.940235048733697</v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>63</v>
       </c>
@@ -15609,7 +15609,7 @@
         <v>115.715374433435</v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>63</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>138.71084192370901</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>63</v>
       </c>
@@ -15663,7 +15663,7 @@
         <v>69.158878504672202</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>65</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>64.369660262322896</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>65</v>
       </c>
@@ -15717,7 +15717,7 @@
         <v>92.707873731497997</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>65</v>
       </c>
@@ -15744,7 +15744,7 @@
         <v>177.39761742408899</v>
       </c>
     </row>
-    <row r="533" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>242</v>
       </c>
@@ -15772,7 +15772,7 @@
         <v>1.8355423310855601</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>243</v>
       </c>
@@ -15800,7 +15800,7 @@
         <v>29.856026685612399</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>244</v>
       </c>
@@ -15828,7 +15828,7 @@
         <v>1.7980490564890901</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>242</v>
       </c>
@@ -15856,7 +15856,7 @@
         <v>51.360282136379098</v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>243</v>
       </c>
@@ -15884,7 +15884,7 @@
         <v>83540.103002551798</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>244</v>
       </c>
@@ -15912,7 +15912,7 @@
         <v>6129.8801677706197</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>242</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>943.53847748515898</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>243</v>
       </c>
@@ -15968,7 +15968,7 @@
         <v>58943.061903343398</v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>244</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>851.70355803861105</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>242</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>276.890268419591</v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>243</v>
       </c>
@@ -16052,7 +16052,7 @@
         <v>19215.595418696201</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>244</v>
       </c>
@@ -16080,7 +16080,7 @@
         <v>4684.6060713342404</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>242</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>228.68947209403299</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>243</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>4808.1587537918404</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>244</v>
       </c>
@@ -16161,7 +16161,7 @@
         <v>9168.7176390797704</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>243</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>113.28734267102701</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>244</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>4130.6542609202297</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>243</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>54.750973553362897</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>244</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>7949.4988499372903</v>
       </c>
     </row>
-    <row r="552" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>245</v>
       </c>
@@ -16301,7 +16301,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>245</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>1408000</v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>245</v>
       </c>
@@ -16357,7 +16357,7 @@
         <v>2818000</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>245</v>
       </c>
@@ -16385,7 +16385,7 @@
         <v>383.1</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>246</v>
       </c>
@@ -16413,7 +16413,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>246</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>582500</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>246</v>
       </c>
@@ -16468,7 +16468,7 @@
         <v>1658000</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>246</v>
       </c>
@@ -16496,7 +16496,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>247</v>
       </c>
@@ -16523,7 +16523,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>247</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>1327000</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>247</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>2031000</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>247</v>
       </c>
@@ -16604,7 +16604,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="564" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>252</v>
       </c>
@@ -16631,7 +16631,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>252</v>
       </c>
@@ -16658,7 +16658,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>252</v>
       </c>
@@ -16685,7 +16685,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>252</v>
       </c>
@@ -16712,7 +16712,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>252</v>
       </c>
@@ -16739,7 +16739,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>252</v>
       </c>
@@ -16766,7 +16766,7 @@
         <v>11.08</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>252</v>
       </c>
@@ -16793,7 +16793,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>252</v>
       </c>
@@ -16820,7 +16820,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>234</v>
       </c>
@@ -16847,7 +16847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="573" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>234</v>
       </c>
@@ -16874,7 +16874,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>234</v>
       </c>
@@ -16901,7 +16901,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>234</v>
       </c>
@@ -16928,7 +16928,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>234</v>
       </c>
@@ -16955,7 +16955,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>234</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="578" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>253</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>5.0159057620259704</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>253</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>569.714248726807</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>253</v>
       </c>
@@ -17063,7 +17063,7 @@
         <v>9415.084904314399</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>253</v>
       </c>
@@ -17090,7 +17090,7 @@
         <v>8913.8882713339208</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>253</v>
       </c>
@@ -17117,7 +17117,7 @@
         <v>6943.0128809192202</v>
       </c>
     </row>
-    <row r="583" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>255</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>2.7825594022071201</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>255</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>53.505085418733202</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>255</v>
       </c>
@@ -17201,7 +17201,7 @@
         <v>13287.913432286799</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>255</v>
       </c>
@@ -17229,7 +17229,7 @@
         <v>2035.3634682404199</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>255</v>
       </c>
@@ -17257,7 +17257,7 @@
         <v>1089.0229622637301</v>
       </c>
     </row>
-    <row r="588" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>257</v>
       </c>
@@ -17285,7 +17285,7 @@
         <v>1.3785225007599999</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>257</v>
       </c>
@@ -17313,7 +17313,7 @@
         <v>2.84346744757267</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>257</v>
       </c>
@@ -17341,7 +17341,7 @@
         <v>39.6453518087473</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>257</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>770.93409949018996</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>257</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>7374.0737605496997</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>257</v>
       </c>
@@ -17425,7 +17425,7 @@
         <v>5715.48201160394</v>
       </c>
     </row>
-    <row r="594" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>259</v>
       </c>
@@ -17452,7 +17452,7 @@
         <v>391.24095645155398</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>259</v>
       </c>
@@ -17479,7 +17479,7 @@
         <v>283569.69995563204</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>259</v>
       </c>
@@ -17506,7 +17506,7 @@
         <v>160148.616398871</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>259</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>81323.795818588391</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>259</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>31007.050317474299</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>259</v>
       </c>
@@ -17587,7 +17587,7 @@
         <v>20203.279233481102</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>259</v>
       </c>
@@ -17614,7 +17614,7 @@
         <v>241487.88800838901</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>259</v>
       </c>
@@ -17641,7 +17641,7 @@
         <v>141366.699530613</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>259</v>
       </c>
@@ -17668,7 +17668,7 @@
         <v>55880.915436266907</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>259</v>
       </c>
@@ -17695,7 +17695,7 @@
         <v>21322.938524639198</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>259</v>
       </c>
@@ -17722,7 +17722,7 @@
         <v>3213.7068680277603</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>259</v>
       </c>
@@ -17749,7 +17749,7 @@
         <v>41.373410807913601</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>259</v>
       </c>
